--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.39208674158938</v>
+        <v>11.11371409550827</v>
       </c>
       <c r="D2" t="n">
-        <v>65.65267232815381</v>
+        <v>10.66855925332499</v>
       </c>
       <c r="E2" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F2" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.03589286738188</v>
+        <v>8.130832590949556</v>
       </c>
       <c r="D3" t="n">
-        <v>50.46595424774402</v>
+        <v>8.200717565258405</v>
       </c>
       <c r="E3" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F3" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.04454290315007</v>
+        <v>8.619738221761887</v>
       </c>
       <c r="D4" t="n">
-        <v>50.89734722307767</v>
+        <v>8.270818923750122</v>
       </c>
       <c r="E4" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F4" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.68746255767699</v>
+        <v>6.124212665622511</v>
       </c>
       <c r="D5" t="n">
-        <v>40.95636452936039</v>
+        <v>6.655409236021063</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F5" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.33799447159788</v>
+        <v>4.279924101634656</v>
       </c>
       <c r="D6" t="n">
-        <v>22.75623598738527</v>
+        <v>3.697888347950107</v>
       </c>
       <c r="E6" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F6" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.63137537801084</v>
+        <v>5.627598498926762</v>
       </c>
       <c r="D7" t="n">
-        <v>31.75411306128946</v>
+        <v>5.160043372459537</v>
       </c>
       <c r="E7" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F7" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.20921918240104</v>
+        <v>7.021498117140169</v>
       </c>
       <c r="D8" t="n">
-        <v>46.70886129109152</v>
+        <v>7.590189959802372</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F8" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.62878253487213</v>
+        <v>5.627177161916721</v>
       </c>
       <c r="D9" t="n">
-        <v>33.18373073526269</v>
+        <v>5.392356244480188</v>
       </c>
       <c r="E9" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F9" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.52486134154718</v>
+        <v>9.185289968001417</v>
       </c>
       <c r="D10" t="n">
-        <v>59.30867905426408</v>
+        <v>9.637660346317913</v>
       </c>
       <c r="E10" t="n">
-        <v>12.4279231650587</v>
+        <v>2.019537514322038</v>
       </c>
       <c r="F10" t="n">
-        <v>13.01212558688709</v>
+        <v>2.114470407869153</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
